--- a/光伏配储项目/电价数据/2026/番禺站.xlsx
+++ b/光伏配储项目/电价数据/2026/番禺站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.53699</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.42933</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.66961</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.23538</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.9746699999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.87663</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44459</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46021</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.4404</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42437</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.45533</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40996</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40303</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38784</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42875</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41538</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41975</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39382</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42813</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4267</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41435</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47696</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>1.01101</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.7697200000000001</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.63229</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.55087</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.74172</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.7732100000000001</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.01131</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.00237</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.05849</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.04505</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05211</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.60111</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.19528</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.18937</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21323</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22679</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.9834299999999999</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.01289</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.20119</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.66886</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.7724500000000001</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>1.08276</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>1.00117</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.32996</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.7759400000000001</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.58775</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.18701</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.84263</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.18595</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.43235</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.25871</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.78555</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.47773</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.22377</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.52197</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.23929</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.68251</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.39841</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.3713</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.35106</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.84477</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47917</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40659</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42175</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.28499</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.02453</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.05845</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53628</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52271</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50629</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.57878</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.5000599999999999</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47428</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.41028</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42319</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.55275</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.76354</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72566</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.46195</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.43262</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1.06707</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.16009</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.80138</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.80828</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.99987</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.00712</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.80184</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.54257</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.5018899999999999</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.21786</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.5703</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.5001100000000001</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.1817</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.41484</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.3056</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>1.25372</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.70033</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.18453</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.80677</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.8060900000000001</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.5009</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.7091000000000001</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.50837</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.51888</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.58396</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.22851</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.17001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.18815</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.14297</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.24536</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.1984</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19568</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.34116</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.79238</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.364</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.55367</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.42338</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>1.03313</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7766000000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.93372</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44054</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42509</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33337</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5168200000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.47225</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5421900000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.43311</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44171</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41708</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.40404</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43529</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45213</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47487</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45083</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44552</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.74274</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.6625700000000001</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.8180299999999999</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.65887</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7845</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.67464</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.46974</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.66443</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.8426900000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.0256</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.55513</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.78247</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.17986</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.18794</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.85425</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.09717</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>1.15631</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>1.18808</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.26297</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.22813</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.7828999999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.45733</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.38401</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.40743</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.52332</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.07159</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.05331</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.25271</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.79493</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.18647</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.18646</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.18666</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.23096</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.18628</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.18376</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.79941</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.79897</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.18266</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.18631</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.56727</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.38669</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.18558</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.10325</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.12412</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.11019</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.29368</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.13434</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.31628</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.11824</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.7996</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.79959</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.5718099999999999</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34315</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.14958</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.70797</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.4956</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.5351699999999999</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.6084299999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.59066</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.58754</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.37495</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46964</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.6511699999999999</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.55249</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.6786799999999999</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.10104</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.1517</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.86275</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.19011</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.45518</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.64934</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.9775900000000001</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.20559</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.21353</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.56201</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.1483</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.2328</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.1473</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.18473</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.6998799999999999</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.65152</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>1.01114</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.65099</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.64288</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.20494</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.03373</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.18726</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.07644</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.77164</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.7355900000000001</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.24055</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.73527</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.14492</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.18671</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.74209</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.03034</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.0097</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.8217000000000001</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.12333</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.18667</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.16206</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.23453</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.16499</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.18645</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.18535</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18569</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.16332</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.18655</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.18656</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.15372</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.86711</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.7271599999999999</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.5018899999999999</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.7523099999999999</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31194</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.5724199999999999</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.50514</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40629</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.2253</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.22076</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.26377</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.26246</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.19378</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.24377</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.26136</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.42393</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.50483</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.19222</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.43057</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.18748</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.50239</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.41645</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18829</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.26642</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.25841</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.29609</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.19411</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.18503</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.39794</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.41409</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.6350399999999999</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.50217</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.49403</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.40408</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.49453</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.49759</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.6130800000000001</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40727</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.49848</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.51118</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.49277</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.40199</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40905</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34638</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.22577</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1.00401</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.02864</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.60149</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.57489</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.40142</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.41876</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.37232</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04613</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.17043</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04425</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.0418</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01117</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20746</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05035</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04343</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.15822</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.06236999999999999</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.01469</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04234</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.16868</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.16926</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.27258</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.19004</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.02372</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.17989</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.18332</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.24419</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.27783</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.24787</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.41143</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.41171</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.26846</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.49197</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.39568</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.43513</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33833</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3908</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.29158</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28903</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.23554</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.27149</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.6519400000000001</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.78898</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.58024</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.55435</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>-0.01083</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.6546900000000001</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.85503</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.7120599999999999</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48496</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.75064</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.75386</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.91962</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.6205000000000001</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.55104</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.41173</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.45876</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.22992</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.23336</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.24268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.67835</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.75602</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.65877</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.61712</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4807</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.74287</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.81828</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.79315</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.7575599999999999</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.03926</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.43773</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.86575</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.47158</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.66515</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.83784</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.42436</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.05776</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.41887</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.47874</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.8019299999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8109299999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7876599999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7934500000000001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88434</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.51189</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.42385</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.47128</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.23095</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63934</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5442</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50601</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45964</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42815</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45271</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45462</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42299</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40499</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45276</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5954400000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.54986</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.11688</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.47122</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43352</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.63282</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.31456</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.28986</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.30064</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.55262</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.82428</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.47882</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.5500499999999999</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.9976799999999999</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.5660599999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.50181</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.44829</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1.02991</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.84458</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.76297</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.6491699999999999</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.4318</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.6177</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.60241</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.6414099999999999</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.7270399999999999</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.6030800000000001</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.64009</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.7585499999999999</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.5994299999999999</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.64718</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.6354500000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.5415800000000001</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.62449</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.65803</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.79052</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.64115</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.7727200000000001</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.65651</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.6479600000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.64924</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.62591</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.60797</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.67544</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.60722</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.49801</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41456</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45409</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41691</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35488</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95602</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.57136</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39822</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41161</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.40305</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40136</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.7436699999999999</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.6429400000000001</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.87863</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.7560800000000001</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.98509</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>1.18739</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.52028</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.44417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.83873</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.93035</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.86486</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.9398</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.83177</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.97637</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.42211</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.58646</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.49825</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.44251</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28296</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3788</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.9114</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.48757</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.89873</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>1.36219</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.24766</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.8138500000000001</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.8370599999999999</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.6249199999999999</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.18809</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>1.03521</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.51636</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.5348999999999999</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.39735</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.07794</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.74418</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.36922</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7035800000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7953300000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.76278</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.44007</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.7801900000000001</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.20057</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>1.23586</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.8263400000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.8876499999999999</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.49739</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.54213</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.67071</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.38112</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.53645</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.47729</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.44273</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.19275</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.6447</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.57926</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.52255</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.90335</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>1.17347</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.56032</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>1.05883</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.20378</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.03717</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>1.07817</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>1.1871</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>1.13712</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.38779</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.93161</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.7622100000000001</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.9636399999999999</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.55002</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.85164</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.92441</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.94931</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.81602</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.8390700000000001</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.527</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.82389</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.8872100000000001</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.9996699999999999</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.78524</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.7728700000000001</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.73581</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.9534199999999999</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.50877</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.85966</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.91142</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.62234</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32482</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43425</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.33855</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>1.39585</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>1.35348</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>1.31386</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.31493</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>1.41893</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.76047</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.66089</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.24807</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.27144</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.55086</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.4055</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45106</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45071</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43991</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40425</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.26563</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.23377</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.24587</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.16273</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.18562</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.19359</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29059</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.27932</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.27681</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.26495</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26568</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.39126</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.43643</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.59648</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.5314800000000001</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.64835</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.88547</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.33782</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.22486</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8881</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45768</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.43345</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.72464</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.98084</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.2241</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.17315</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.07268</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.55464</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.44276</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39179</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49909</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.41621</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.39675</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41875</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1.49933</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.42943</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.59592</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.7482300000000001</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.74595</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>1.73468</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.73585</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.64774</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.41038</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.99125</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.02775</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.58727</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.06149</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.42505</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.30344</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.36344</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.70862</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.22111</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.14992</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.67338</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.28265</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.57908</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.44445</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.42747</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.46122</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.4746</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.46964</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.44654</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.47105</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.19445</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.50388</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.73654</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.58588</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.61786</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.50136</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.50916</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.51734</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.45221</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.55165</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.07023</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.18715</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.4952</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.50368</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.49739</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.52725</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.67378</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>1.13199</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>1.07083</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.41541</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.42183</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.32676</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.4372</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.79287</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.5977899999999999</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.48618</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.44565</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.44826</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.75417</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.28504</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.95972</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.94453</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.79637</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.4583</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.42236</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.5046</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.45036</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39321</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40303</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34927</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.21915</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.27704</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.23628</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.21717</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.11481</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.26246</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.59757</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.38791</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.44849</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.20816</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.43732</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56821</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.40068</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.4143</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38524</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6517200000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83199</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47226</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40375</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3448</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1.1877</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1.18815</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1.18827</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.18781</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>1.18713</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>1.1867</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>1.18532</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>1.18001</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>1.48729</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>1.39578</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>1.18683</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>1.18669</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.49267</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>1.51664</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>1.55289</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>1.2564</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>1.18675</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>1.18686</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>1.18685</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>1.18681</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>1.18684</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>1.18685</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>1.18682</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>1.21692</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>1.18713</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>1.18385</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>1.1867</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>1.17167</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>1.18706</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>1.18732</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>1.18726</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.46222</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.06601</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.59095</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.51835</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.17451</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.18095</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.1757</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.1736</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.17938</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.07395</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.24601</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.19415</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.1952</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.18711</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.85875</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.23117</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.8855700000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.38784</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.97012</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.8071499999999999</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.99403</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.72057</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.9458799999999999</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.18851</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.9029299999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43158</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42054</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>1.33242</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1.44916</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.37444</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1.41949</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.41698</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40658</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1.34729</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4119</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1.40168</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1.22937</v>
+      </c>
+      <c r="O133" t="n">
+        <v>1.24514</v>
+      </c>
+      <c r="P133" t="n">
+        <v>1.2489</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>1.2093</v>
+      </c>
+      <c r="R133" t="n">
+        <v>1.25683</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40089</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41377</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>1.26707</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>1.2365</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.36751</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>1.31315</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.26724</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>1.56631</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>1.44507</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.73255</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.63389</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.76597</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>1.14649</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>1.20268</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.41327</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.57308</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.23992</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.5906</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>1.1876</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.5386</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.65634</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.6769700000000001</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.9343400000000001</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.18725</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.83478</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1.19931</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.84868</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>1.2179</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>1.1991</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.27794</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.23743</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.9279700000000001</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.9291699999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.30793</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.48505</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.74509</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.56421</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.6933</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.8289299999999999</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47409</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41955</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.33894</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.7118300000000001</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45491</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.4588</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43704</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.43057</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.52801</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>1.1866</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.18681</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>1.18559</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.18673</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>1.18714</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>1.18441</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1.18806</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.18783</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>1.18772</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>1.19766</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.59261</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.69427</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.5898</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.18247</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.59789</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.48105</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.02775</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.52758</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.00369</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5382899999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.58758</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.43448</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.2244</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.60322</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.5790700000000001</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.69869</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51701</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46366</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.48951</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.70266</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.70425</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.9189700000000001</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40316</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39384</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36412</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.6403799999999999</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.84178</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.50497</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.40954</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.40149</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1.20137</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1.1821</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>1.18725</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>1.1871</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.19987</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25829</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.19749</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.25696</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.26999</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.20801</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.25618</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.28873</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.28703</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.24548</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.27022</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.40982</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.68015</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.55625</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.40387</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.42505</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.6368200000000001</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.38496</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.49124</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42794</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.39451</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.39746</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.4329</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35202</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.3022</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1.17428</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.20323</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25987</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.20136</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.24711</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.24016</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.19828</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.18261</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.21146</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.17766</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.1966</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.17646</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>1.17506</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>1.17506</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.17209</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.19277</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.17923</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.17169</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.20001</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.41019</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.17029</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.1789</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.17031</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.43867</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.17422</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.18015</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.24638</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.64064</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.3277</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.84502</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.87815</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.20038</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.49761</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.41383</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.5588500000000001</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.53054</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.42288</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.42057</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.6236900000000001</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.56692</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.48475</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.28006</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.47172</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.42121</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.69602</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.05427000000000001</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.04607</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.48466</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.17702</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.03633</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.5938</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.48395</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.17505</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.46306</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>1.0293</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.7935800000000001</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.36258</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>1.21221</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1.1984</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>1.17503</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>1.17514</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.17518</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.7414500000000001</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>1.24973</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>1.1751</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>1.29618</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.74286</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.74778</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.74335</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.79314</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.76069</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.79067</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.33483</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.2529</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.57459</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>1.55985</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>1.53686</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.59604</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33773</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1.17561</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.17423</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.17799</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.59748</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.59842</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.4744</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.41768</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.41123</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.27256</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.38786</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.39513</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.50962</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5296900000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.4536</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>1.17484</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>1.17519</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>1.1753</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>1.1753</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>1.17504</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.82697</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.65657</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.5696</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.65917</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.58033</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.59889</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>1.18361</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.5708300000000001</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5779</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.9193300000000001</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.8783200000000001</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.45652</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.56641</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.53173</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.17503</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.8108500000000001</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.45861</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.42034</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.41979</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.43212</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.42331</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.43802</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.48179</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.47799</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.47804</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.43808</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.44845</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.39573</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.44327</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.47545</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.54157</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.17513</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.17623</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.5521699999999999</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.48145</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.8530800000000001</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.6763400000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.5569500000000001</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.17687</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>1.17373</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.5108199999999999</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.45228</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.44201</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.46572</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33931</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.43734</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.41883</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.38408</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>1.30319</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>1.26713</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>1.1826</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1.17523</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.63263</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.67786</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>1.17506</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.17474</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>1.17487</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>1.224</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>1.17868</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>1.19978</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>1.20624</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.17297</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.5787</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.17336</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.69664</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.1757</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.76595</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.25311</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.74782</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>1.17466</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>1.17488</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>1.17487</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>1.17466</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.33298</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.73468</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.61259</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.54862</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.8940900000000001</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.54772</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.64917</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.44344</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>1.17507</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>1.17625</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>1.17793</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>1.17453</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42442</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6930499999999999</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>1.17343</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45854</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.58188</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>1.36614</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>1.17515</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1.08297</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>1.17511</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36871</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1.17513</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1.1761</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1.17614</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>1.18547</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>1.17404</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1.17455</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.47111</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.44879</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.39296</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.63829</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.33174</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>1.17459</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.25291</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.40735</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.2606</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.24347</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.24368</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.37559</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.29325</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.22249</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>1.63345</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>1.17486</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>1.17513</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>1.17474</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>1.17534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>1.17485</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.86391</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>1.17525</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.07185</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.63711</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.36045</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.26104</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.45781</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.18366</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.51267</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.4923</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.76584</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.53357</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.6722100000000001</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.84502</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.6432</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37513</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27104</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1.17475</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.6017</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.42888</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.44831</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.8457</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.38003</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.04991</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9801599999999999</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.00632</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.02925</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.17353</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.99425</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.91022</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.7227899999999999</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.08151</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.17669</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.17524</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.22544</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.92835</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.20032</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.7495700000000001</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.17615</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.49834</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.17703</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.17665</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.1781</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.17543</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.5464199999999999</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.26939</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>1.17461</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.8512000000000001</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.17599</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>1.17708</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>1.18219</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.24865</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>1.30904</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.10046</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.22113</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.1152</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.1856</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.09668</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.10729</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.20381</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.21102</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.22984</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.19956</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.16612</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.14685</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.17456</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.22581</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.24596</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.22633</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>1.17431</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>1.17386</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>1.17425</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>1.17426</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>1.17435</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37568</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>1.35046</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.36791</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.57353</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.11363</v>
+      </c>
+      <c r="H142" t="n">
+        <v>1.1746</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1.24451</v>
+      </c>
+      <c r="J142" t="n">
+        <v>1.23189</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="L142" t="n">
+        <v>1.58149</v>
+      </c>
+      <c r="M142" t="n">
+        <v>1.37707</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.8461000000000001</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.9007200000000001</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>1.2183</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.23848</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>1.17489</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.47958</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>1.27866</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1.48489</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.72886</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.31486</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.49589</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.76814</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.72576</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.96774</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.24002</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.18279</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.16325</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.23717</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.79513</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.16675</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.54096</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>1.16031</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.69914</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1.14112</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>1.17026</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.99058</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.20017</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.20668</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.84749</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.18288</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.80008</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.93662</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.84982</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.18345</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.1778</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.18487</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.18731</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.1913</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.18798</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.67012</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.1956</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.19209</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.19044</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.18693</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.19146</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.19064</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.58935</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.1979</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.1728</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.5967899999999999</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.31611</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.40554</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.5377</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.9543700000000001</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.56071</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.42546</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.18813</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1.17546</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.49454</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1.17528</v>
+      </c>
+      <c r="H143" t="n">
+        <v>1.1753</v>
+      </c>
+      <c r="I143" t="n">
+        <v>1.17509</v>
+      </c>
+      <c r="J143" t="n">
+        <v>1.17533</v>
+      </c>
+      <c r="K143" t="n">
+        <v>1.17526</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.40368</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.21312</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.41455</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.40568</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.84517</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.1752</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>1.17471</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>1.17568</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.43391</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>1.17528</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1.17607</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>1.17552</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>1.21966</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.59511</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>1.30915</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>1.46167</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>1.30563</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>1.66178</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>1.41283</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>1.17459</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>1.1739</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.21529</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>1.17373</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>1.17477</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.41091</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.17494</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.17652</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.17551</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>1.17532</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>1.17501</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>1.17454</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>1.1778</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>1.17854</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>1.17879</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>1.17901</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>1.18308</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>1.18865</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.18191</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>1.18308</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.18226</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.18023</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>1.18315</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>1.18825</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>1.18506</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.77389</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.50282</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>1.18924</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>1.19523</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>1.18902</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>1.18814</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>1.18314</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>1.18509</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.42265</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40858</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40974</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
